--- a/data/dividends_info_20260904.xlsx
+++ b/data/dividends_info_20260904.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>44.93000030517578</v>
+        <v>44.80500030517578</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2003115944551469</v>
+        <v>0.2008704371989556</v>
       </c>
       <c r="J2" t="n">
         <v>192</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>66.15000152587891</v>
+        <v>66</v>
       </c>
       <c r="I3" t="n">
-        <v>1.058201033791585</v>
+        <v>1.060606060606061</v>
       </c>
       <c r="J3" t="n">
         <v>171</v>
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.4939999878406525</v>
+        <v>0.5099999904632568</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8097166191206999</v>
+        <v>0.784313740156468</v>
       </c>
       <c r="J5" t="n">
         <v>101</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>44.93000030517578</v>
+        <v>44.80500030517578</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2003115944551469</v>
+        <v>0.2008704371989556</v>
       </c>
       <c r="J6" t="n">
         <v>101</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.085000038146973</v>
+        <v>2.079999923706055</v>
       </c>
       <c r="I7" t="n">
-        <v>3.693045495981532</v>
+        <v>3.701923212708811</v>
       </c>
       <c r="J7" t="n">
         <v>80</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>23.43499946594238</v>
+        <v>23.07500076293945</v>
       </c>
       <c r="I8" t="n">
-        <v>1.1521229193642</v>
+        <v>1.170097469438201</v>
       </c>
       <c r="J8" t="n">
         <v>80</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>24.21999931335449</v>
+        <v>24.15999984741211</v>
       </c>
       <c r="I9" t="n">
-        <v>2.436003372116877</v>
+        <v>2.442052995555783</v>
       </c>
       <c r="J9" t="n">
         <v>80</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>5.829999923706055</v>
+        <v>5.860000133514404</v>
       </c>
       <c r="I10" t="n">
-        <v>3.430531777311974</v>
+        <v>3.412969205515265</v>
       </c>
       <c r="J10" t="n">
         <v>73</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>10.32999992370605</v>
+        <v>10.52000045776367</v>
       </c>
       <c r="I11" t="n">
-        <v>4.453049403653505</v>
+        <v>4.372623383875653</v>
       </c>
       <c r="J11" t="n">
         <v>52</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0.4939999878406525</v>
+        <v>0.5099999904632568</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8097166191206999</v>
+        <v>0.784313740156468</v>
       </c>
       <c r="J13" t="n">
         <v>45</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>5.28000020980835</v>
+        <v>5.300000190734863</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7196969410987827</v>
+        <v>0.7169811062729635</v>
       </c>
       <c r="J15" t="n">
         <v>24</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>23.43499946594238</v>
+        <v>23.07500076293945</v>
       </c>
       <c r="I16" t="n">
-        <v>1.1521229193642</v>
+        <v>1.170097469438201</v>
       </c>
       <c r="J16" t="n">
         <v>17</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1.996999979019165</v>
+        <v>1.991000056266785</v>
       </c>
       <c r="I17" t="n">
-        <v>2.854281452120786</v>
+        <v>2.862882892473523</v>
       </c>
       <c r="J17" t="n">
         <v>17</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>44.93000030517578</v>
+        <v>44.80500030517578</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2003115944551469</v>
+        <v>0.2008704371989556</v>
       </c>
       <c r="J18" t="n">
         <v>17</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>96.59999847412109</v>
+        <v>97.44999694824219</v>
       </c>
       <c r="I19" t="n">
-        <v>1.376811615950805</v>
+        <v>1.364802505541783</v>
       </c>
       <c r="J19" t="n">
         <v>17</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>6.300000190734863</v>
+        <v>6.28000020980835</v>
       </c>
       <c r="I20" t="n">
-        <v>4.761904617736313</v>
+        <v>4.777069904097268</v>
       </c>
       <c r="J20" t="n">
         <v>10</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>0.4939999878406525</v>
+        <v>0.5099999904632568</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8097166191206999</v>
+        <v>0.784313740156468</v>
       </c>
       <c r="J21" t="n">
         <v>-11</v>
@@ -1486,7 +1486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C234"/>
+  <dimension ref="A1:C304"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2223,7 +2223,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2257,7 +2257,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2267,14 +2267,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -2529,7 +2529,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Somec S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2556,14 +2556,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>Somec S.p.A.</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -2597,7 +2597,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -2631,7 +2631,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>BEEWIZE</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2648,7 +2648,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>BEEWIZE</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2658,7 +2658,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -2682,7 +2682,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>KME Group S.p.A.</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2692,14 +2692,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>RATTI S.p.A. SOCIETA' BENEFIT</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2709,14 +2709,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>WEBSOLUTE S.p.A.</t>
+          <t>RATTI S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2733,7 +2733,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>KME Group S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2743,14 +2743,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>WEBSOLUTE S.p.A.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2760,7 +2760,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -2801,7 +2801,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Confinvest Oro S.p.A.</t>
+          <t>Yakkyo S.p.A.</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2818,7 +2818,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>I.CO.P. S.p.A. Società Benefit</t>
+          <t>RT&amp;L S.P.A.</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2835,7 +2835,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>RT&amp;L S.P.A.</t>
+          <t>I.CO.P. S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2852,7 +2852,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Yakkyo S.p.A.</t>
+          <t>Confinvest Oro S.p.A.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2869,7 +2869,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Ubaldi Costruzioni S.p.A.</t>
+          <t>DHH S.p.A.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2886,7 +2886,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>I.M.D. International Medical Devices S.p.A.</t>
+          <t>GIUNTI PSYCHOMETRICS HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2903,7 +2903,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Italian Wine Brands S.p.A.</t>
+          <t>I.M.D. International Medical Devices S.p.A.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2920,7 +2920,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>DHH S.p.A.</t>
+          <t>Italian Wine Brands S.p.A.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2937,7 +2937,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>GIUNTI PSYCHOMETRICS HOLDING S.p.A.</t>
+          <t>Ubaldi Costruzioni S.p.A.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2954,7 +2954,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>OLIDATA S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2971,7 +2971,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>PHILOGEN S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2988,7 +2988,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>OVS S.p.A.</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3005,7 +3005,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>OVS S.p.A.</t>
+          <t>OPS Italia S.p.A.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3015,14 +3015,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>OPS Italia S.p.A.</t>
+          <t>OLIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3032,14 +3032,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Lindbergh S.p.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3056,7 +3056,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>Lindbergh S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3175,7 +3175,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Impianti S.p.A.</t>
+          <t>POWERSOFT S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3192,7 +3192,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>rino petino S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3209,7 +3209,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>POWERSOFT S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3226,7 +3226,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>Softlab S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3243,7 +3243,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>JUVENTUS F.C. S.p.A.</t>
+          <t>Sicily by Car S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3253,14 +3253,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Giglio.com S.p.A.</t>
+          <t>SIAV S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3277,7 +3277,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>E-NOVIA S.p.A.</t>
+          <t>RES S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3294,7 +3294,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ELSA Solutions S.p.A.</t>
+          <t>Porto Aviation Group S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3311,7 +3311,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>DOTSTAY S.p.A.</t>
+          <t>JUVENTUS F.C. S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3321,14 +3321,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>DIGITAL BROS S.p.A.</t>
+          <t>eVISO S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3345,7 +3345,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
+          <t>Impianti S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3362,7 +3362,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Egomnia S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3379,12 +3379,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Predict S.p.A.</t>
+          <t>Giglio.com S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3396,12 +3396,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>SBE-Varvit S.p.A.</t>
+          <t>Egomnia S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3413,29 +3413,29 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>SIAV S.p.A.</t>
+          <t>ELSA Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Smart Capital S.p.A.</t>
+          <t>E-NOVIA S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -3447,12 +3447,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>DOTSTAY S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -3464,29 +3464,29 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>VINEXT S.p.A.</t>
+          <t>DIGITAL BROS S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>gAIn360 S.p.A.</t>
+          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -3498,29 +3498,29 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A.B.P. Nocivelli S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Telmes S.p.A.</t>
+          <t>VINEXT S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -3532,63 +3532,63 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A.B.P. Nocivelli S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>AEFFE S.p.A.</t>
+          <t>Smart Capital S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Triboo S.p.A.</t>
+          <t>SIAV S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Guidotti Ships S.p.A.</t>
+          <t>SBE-Varvit S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -3600,12 +3600,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Haiki+ S.p.A.</t>
+          <t>Predict S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -3617,12 +3617,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>INNOVATEC S.p.A.</t>
+          <t>Ecomembrane S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -3634,12 +3634,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>Cloudia Research S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -3651,29 +3651,29 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Longino &amp; Cardenal S.p.A.</t>
+          <t>DANIELI &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -3685,12 +3685,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>MARZOCCHI POMPE S.p.A.</t>
+          <t>FOPE S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -3702,12 +3702,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Markbass S.p.A.</t>
+          <t>ILPRA S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -3719,12 +3719,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Metriks AI S.p.A. Società Benefit</t>
+          <t>MIT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -3736,12 +3736,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>YOLO GROUP S.p.A.</t>
+          <t>BESTBE HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -3753,12 +3753,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ZEST S.p.A.</t>
+          <t>gAIn360 S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -3770,12 +3770,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>TradeLab S.p.A.</t>
+          <t>Pasquarelli Auto S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -3787,12 +3787,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>Maps S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -3804,12 +3804,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Franchi Umberto Marmi S.p.A.</t>
+          <t>Allcore S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -3821,12 +3821,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>GPI S.p.A.</t>
+          <t>BASTOGI S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -3838,12 +3838,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>GEL S.p.A.</t>
+          <t>Telmes S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -3855,12 +3855,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>Metriks AI S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -3872,12 +3872,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Gambero Rosso S.p.A.</t>
+          <t>Markbass S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -3889,12 +3889,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
+          <t>MARZOCCHI POMPE S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -3906,12 +3906,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Grifal S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -3923,12 +3923,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
+          <t>Longino &amp; Cardenal S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -3940,12 +3940,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>TradeLab S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -3957,12 +3957,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Copernico SIM S.p.A.</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -3974,12 +3974,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
+          <t>Haiki+ S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -3991,12 +3991,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>Guidotti Ships S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -4008,12 +4008,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
+          <t>Farmacosmo S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -4025,12 +4025,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>COFLE S.p.A.</t>
+          <t>ZEST S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -4042,12 +4042,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Bellini Nautica S.p.A.</t>
+          <t>Triboo S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -4059,63 +4059,63 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>A.B.P. Nocivelli S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Otofarma S.p.A.</t>
+          <t>A.B.P. Nocivelli S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>OPS Italia S.p.A.</t>
+          <t>AEFFE S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Novamarine S.p.A.</t>
+          <t>INNOVATEC S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -4127,12 +4127,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>NOTORIOUS PICTURES S.p.A.</t>
+          <t>YOLO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -4144,12 +4144,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Monnalisa S.p.A.</t>
+          <t>DBA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -4161,12 +4161,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Magis S.p.A.</t>
+          <t>Ambromobiliare S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -4178,12 +4178,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Lemon Sistemi S.p.A.</t>
+          <t>Simone S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -4195,12 +4195,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>International Care Company S.p.A.</t>
+          <t>Redelfi S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -4212,12 +4212,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>iVision Tech S.p.A.</t>
+          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -4229,29 +4229,29 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>PREMIA FINANCE S.P.A</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>OMER S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -4263,12 +4263,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>UCapital24 S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -4280,12 +4280,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>ISCC FINTECH S.p.A.</t>
+          <t>Next Geosolutions Europe S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -4297,12 +4297,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>FRENDY ENERGY S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -4314,12 +4314,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Gens Aurea S.p.A.</t>
+          <t>Estrima S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -4331,12 +4331,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -4348,12 +4348,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>Edil San Felice S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -4365,46 +4365,46 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>FIDIA S.p.A</t>
+          <t>Edil San Felice S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Alfio Bardolla Training Group S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Adventure S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -4416,29 +4416,29 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>ATON Green Storage S.p.A.</t>
+          <t>AEFFE S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>EUKEDOS S.p.A.</t>
+          <t>TMP Group S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -4450,12 +4450,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>ETI S.p.A.</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -4467,12 +4467,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>EPH INVEST S.p.A.</t>
+          <t>T.P.S. S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -4484,7 +4484,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>ENA S.p.A.</t>
+          <t>Monnalisa S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -4501,7 +4501,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -4511,14 +4511,14 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>BORGOSESIA S.p.A.</t>
+          <t>Copernico SIM S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -4535,7 +4535,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>Reti S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -4552,7 +4552,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>ErreDue S.p.A.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -4569,7 +4569,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -4586,7 +4586,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>SOSTRAVEL.COM S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -4603,7 +4603,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -4613,14 +4613,14 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>FAE Technology Società Benefit S.p.A.</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -4637,12 +4637,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>TESSELLIS S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -4654,29 +4654,29 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>Telesia S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -4688,12 +4688,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -4705,12 +4705,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -4722,12 +4722,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Reway Group S.p.A.</t>
+          <t>International Care Company S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -4739,12 +4739,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Pozzi Milano S.p.A.</t>
+          <t>Lemon Sistemi S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -4756,29 +4756,29 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Lucisano Media Group S.p.A.</t>
+          <t>ENA S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -4790,12 +4790,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Litix S.p.A.</t>
+          <t>EPH INVEST S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -4807,12 +4807,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Leone Film Group S.p.A.</t>
+          <t>ETI S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -4824,12 +4824,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Itway S.p.A.</t>
+          <t>EUKEDOS S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -4841,12 +4841,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>IDNTT S.A.</t>
+          <t>PLANETEL S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -4858,12 +4858,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>HELYX INDUSTRIES S.p.A.</t>
+          <t>Otofarma S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -4875,12 +4875,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -4892,12 +4892,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>G.M. Leather S.p.A.</t>
+          <t>OPS Italia S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -4909,12 +4909,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>First Point S.p.A.</t>
+          <t>Novamarine S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -4926,12 +4926,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>Magis S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -4943,12 +4943,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Portobello S.p.A.</t>
+          <t>Misitano &amp; Stracuzzi S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -4960,12 +4960,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Alia Mentis S.p.A.</t>
+          <t>NOTORIOUS PICTURES S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -4977,12 +4977,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>CLASS EDITORI S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -4994,12 +4994,12 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Valica S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -5011,12 +5011,12 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Vantea Smart S.p.A.</t>
+          <t>COFLE S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -5028,12 +5028,12 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Vivenda Group S.p.A.</t>
+          <t>UCapital24 S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -5045,12 +5045,12 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>doxee S.p.A.</t>
+          <t>iVision Tech S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -5062,12 +5062,12 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>ECOSUNTEK S.p.A.</t>
+          <t>ISCC FINTECH S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -5079,12 +5079,12 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>ESPE S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -5096,12 +5096,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>EXPERT.AI S.p.A.</t>
+          <t>Grifal S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -5113,12 +5113,12 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>EdgeLab S.p.A.</t>
+          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -5130,12 +5130,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Emma Villas S.p.A.</t>
+          <t>Gambero Rosso S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -5147,29 +5147,29 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>FIDIA S.p.A</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Piu' Medical S.p.A.</t>
+          <t>FAE Technology Società Benefit S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -5181,12 +5181,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Eprcomunicazione S.p.A. Società Benefit</t>
+          <t>ErreDue S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -5198,12 +5198,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -5215,29 +5215,29 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>FRANCHETTI S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Finanza.tech S.p.A. Società Benefit</t>
+          <t>Gens Aurea S.p.A.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -5249,12 +5249,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Tenax International S.p.A.</t>
+          <t>GPI S.p.A.</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -5266,12 +5266,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>TRAWELL CO S.p.A.</t>
+          <t>Bellini Nautica S.p.A.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -5283,29 +5283,29 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Solid World Group S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Società Editoriale il Fatto S.p.A.</t>
+          <t>Rocket Sharing Company S.p.A.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -5317,12 +5317,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>AATECH S.p.A. Società Benefit</t>
+          <t>BORGOSESIA S.p.A.</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -5334,12 +5334,12 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>ABC Company S.p.A. Società Benefit</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -5351,12 +5351,12 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>ACQUAZZURRA S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -5368,29 +5368,29 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>The Italian Sea Group S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>B.F. S.p.A.</t>
+          <t>GEL S.p.A.</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -5402,12 +5402,12 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Execus S.p.A.</t>
+          <t>Franchi Umberto Marmi S.p.A.</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -5419,51 +5419,1241 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>Adventure S.p.A.</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>LANDI RENZO S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
+          <t>Alfio Bardolla Training Group S.p.A.</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>ATON Green Storage S.p.A.</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>B.F. S.p.A.</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>AATECH S.p.A. Società Benefit</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>ABC Company S.p.A. Società Benefit</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>ACQUAZZURRA S.p.A.</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Alia Mentis S.p.A.</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Officina Stellare S.p.A.</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>OPS ECOM S.p.A.</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Met.Extra Group S.p.A.</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>MONDO TV S.p.A.</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>MONDO TV FRANCE</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>MEVIM S.p.A.</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>CLASS EDITORI S.p.A.</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>OPT S.p.A.</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Matica Fintec S.p.A.</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>PROMOTICA S.p.A.</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Vivenda Group S.p.A.</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>ECOSUNTEK S.p.A.</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Lucisano Media Group S.p.A.</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Litix S.p.A.</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Leone Film Group S.p.A.</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>KALEON S.P.A.</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Itway S.p.A.</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>IDNTT S.A.</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>HELYX INDUSTRIES S.p.A.</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Gentili Mosconi S.p.A.</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>G.M. Leather S.p.A.</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>ESPE S.p.A.</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>First Point S.p.A.</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Reway Group S.p.A.</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Renovalo S.p.A.</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>RedFish LongTerm Capital S.p.A.</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Racing Force S.p.A.</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Analyst Presentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>ROSETTI MARINO S.p.A.</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Pozzi Milano S.p.A.</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Portobello S.p.A.</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Piu' Medical S.p.A.</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>PLC S.p.A.</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>doxee S.p.A.</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>EXPERT.AI S.p.A.</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Emma Villas S.p.A.</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>The Italian Sea Group S.p.A.</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Tenax International S.p.A.</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>TRAWELL CO S.p.A.</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Solid World Group S.p.A.</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Società Editoriale il Fatto S.p.A.</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>E-Globe S.p.A.</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Dipietro Group S.p.A.</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Vantea Smart S.p.A.</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>Dedem S.p.A.</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>EdgeLab S.p.A.</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>VNE S.p.A.</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>DESTINATION ITALIA S.p.A.</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Cube Labs S.p.A.</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Com.Tel S.p.A.</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>Cogefeed S.p.A.</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>CleanBnB S.p.A.</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>Casta Diva Group S.p.A.</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>Finanza.tech S.p.A. Società Benefit</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>FRANCHETTI S.p.A.</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>Execus S.p.A.</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>Eprcomunicazione S.p.A. Società Benefit</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>Energy Time S.p.A.</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Analyst Presentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>DEODATO.GALLERY S.p.A.</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>Valica S.p.A.</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Half Year Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
           <t>S.S. Lazio S.p.A.</t>
         </is>
       </c>
-      <c r="B234" t="inlineStr">
+      <c r="B302" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C234" t="inlineStr">
+      <c r="C302" t="inlineStr">
         <is>
           <t>SB Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>LANDI RENZO S.p.A.</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>Renovalo S.p.A.</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -5491,44 +6681,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Stellantis N.V.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>